--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.3550,0.4918,0.0265,0.1804</t>
-  </si>
-  <si>
-    <t>0.0195,0.0030,0.0007,0.9929</t>
-  </si>
-  <si>
-    <t>0.5345,0.0682,0.0266,0.4421</t>
-  </si>
-  <si>
-    <t>0.1063,0.0192,0.0014,0.9604</t>
-  </si>
-  <si>
-    <t>0.9952,0.0019,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9918,0.0061,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9859,0.0056,0.0016,0.0029</t>
-  </si>
-  <si>
-    <t>0.9895,0.0034,0.0013,0.0025</t>
-  </si>
-  <si>
-    <t>0.9845,0.0175,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9785,0.0187,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.9947,0.0015,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9941,0.0014,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.6847,0.0376,0.3029,0.0061</t>
-  </si>
-  <si>
-    <t>0.3995,0.0547,0.5996,0.0284</t>
-  </si>
-  <si>
-    <t>0.1635,0.0193,0.8661,0.0016</t>
-  </si>
-  <si>
-    <t>0.2547,0.0100,0.7963,0.0007</t>
-  </si>
-  <si>
-    <t>0.3818,0.0412,0.6272,0.0066</t>
-  </si>
-  <si>
-    <t>0.0111,0.9865,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.0126,0.9867,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.4987,0.5994,0.0128,0.0035</t>
-  </si>
-  <si>
-    <t>0.3052,0.8383,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.9935,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.4891,0.0057,0.6101,0.0070</t>
-  </si>
-  <si>
-    <t>0.5191,0.0322,0.4396,0.0307</t>
-  </si>
-  <si>
-    <t>0.0211,0.0073,0.9733,0.0036</t>
-  </si>
-  <si>
-    <t>0.2424,0.0699,0.6686,0.0039</t>
-  </si>
-  <si>
-    <t>0.0588,0.1224,0.8875,0.0062</t>
-  </si>
-  <si>
-    <t>0.1842,0.0121,0.7442,0.0783</t>
-  </si>
-  <si>
-    <t>0.0030,0.0009,0.9940,0.0028</t>
-  </si>
-  <si>
-    <t>0.0915,0.9067,0.0174,0.0011</t>
-  </si>
-  <si>
-    <t>0.2736,0.0589,0.7249,0.0038</t>
-  </si>
-  <si>
-    <t>0.0010,0.0060,0.9960,0.0018</t>
-  </si>
-  <si>
-    <t>0.0445,0.8163,0.4338,0.0050</t>
-  </si>
-  <si>
-    <t>0.6860,0.2036,0.1289,0.0211</t>
-  </si>
-  <si>
-    <t>0.7896,0.0541,0.1438,0.0057</t>
-  </si>
-  <si>
-    <t>0.5229,0.5003,0.0308,0.0010</t>
-  </si>
-  <si>
-    <t>0.2489,0.7776,0.0894,0.0037</t>
-  </si>
-  <si>
-    <t>0.0506,0.6861,0.4678,0.0686</t>
-  </si>
-  <si>
-    <t>0.0641,0.0423,0.9246,0.0058</t>
-  </si>
-  <si>
-    <t>0.0165,0.2104,0.9284,0.0081</t>
-  </si>
-  <si>
-    <t>0.1269,0.0139,0.8849,0.0060</t>
-  </si>
-  <si>
-    <t>0.0099,0.0483,0.9745,0.0055</t>
-  </si>
-  <si>
-    <t>0.0156,0.9499,0.1040,0.0031</t>
-  </si>
-  <si>
-    <t>0.0761,0.0292,0.9113,0.0058</t>
-  </si>
-  <si>
-    <t>0.0381,0.8347,0.0384,0.6646</t>
-  </si>
-  <si>
-    <t>0.0040,0.9715,0.0382,0.0300</t>
-  </si>
-  <si>
-    <t>0.0063,0.9577,0.3650,0.0021</t>
-  </si>
-  <si>
-    <t>0.0018,0.9885,0.0469,0.0024</t>
-  </si>
-  <si>
-    <t>0.0036,0.1097,0.9854,0.0009</t>
-  </si>
-  <si>
-    <t>0.0038,0.6151,0.9450,0.0008</t>
-  </si>
-  <si>
-    <t>0.0322,0.0674,0.9254,0.0061</t>
-  </si>
-  <si>
-    <t>0.1589,0.0093,0.8631,0.0120</t>
-  </si>
-  <si>
-    <t>0.0108,0.0050,0.9835,0.0041</t>
-  </si>
-  <si>
-    <t>0.0021,0.0072,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.9448,0.0763,0.0038,0.0024</t>
-  </si>
-  <si>
-    <t>0.9193,0.0266,0.0435,0.0130</t>
-  </si>
-  <si>
-    <t>0.9599,0.0129,0.0077,0.0157</t>
-  </si>
-  <si>
-    <t>0.0267,0.2326,0.9197,0.0053</t>
-  </si>
-  <si>
-    <t>0.9624,0.0285,0.0069,0.0053</t>
-  </si>
-  <si>
-    <t>0.9869,0.0058,0.0033,0.0015</t>
-  </si>
-  <si>
-    <t>0.9568,0.0319,0.0080,0.0046</t>
-  </si>
-  <si>
-    <t>0.0012,0.8105,0.9453,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0255,0.9938,0.0012</t>
-  </si>
-  <si>
-    <t>0.0057,0.1065,0.9618,0.0052</t>
-  </si>
-  <si>
-    <t>0.0033,0.7544,0.9080,0.0024</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0422,0.9368,0.0290,0.0015</t>
-  </si>
-  <si>
-    <t>0.0075,0.9893,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9039,0.0330,0.0588,0.0069</t>
-  </si>
-  <si>
-    <t>0.2647,0.1348,0.6797,0.0059</t>
-  </si>
-  <si>
-    <t>0.0317,0.0663,0.9518,0.0126</t>
-  </si>
-  <si>
-    <t>0.0010,0.8107,0.9448,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9034,0.7717,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9624,0.6208,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9348,0.7132,0.0008</t>
-  </si>
-  <si>
-    <t>0.0030,0.0008,0.0875,0.9634</t>
-  </si>
-  <si>
-    <t>0.0042,0.0046,0.0003,0.9978</t>
-  </si>
-  <si>
-    <t>0.0012,0.0769,0.0020,0.9969</t>
-  </si>
-  <si>
-    <t>0.0103,0.0027,0.0015,0.9942</t>
-  </si>
-  <si>
-    <t>0.0099,0.0014,0.0008,0.9950</t>
-  </si>
-  <si>
-    <t>0.0093,0.0045,0.0026,0.9936</t>
-  </si>
-  <si>
-    <t>0.0001,0.9578,0.9236,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.6457,0.9856,0.0002</t>
-  </si>
-  <si>
-    <t>0.0283,0.5415,0.7546,0.0061</t>
-  </si>
-  <si>
-    <t>0.0115,0.5646,0.8325,0.0016</t>
-  </si>
-  <si>
-    <t>0.0022,0.9615,0.3714,0.0001</t>
-  </si>
-  <si>
-    <t>0.0048,0.7299,0.8993,0.0011</t>
-  </si>
-  <si>
-    <t>0.9859,0.0119,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9876,0.0097,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.9817,0.0230,0.0018,0.0007</t>
-  </si>
-  <si>
-    <t>0.9947,0.0026,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9806,0.0127,0.0023,0.0033</t>
-  </si>
-  <si>
-    <t>0.9952,0.0030,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0105,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9795,0.0202,0.0025,0.0014</t>
-  </si>
-  <si>
-    <t>0.9935,0.0011,0.0004,0.0023</t>
-  </si>
-  <si>
-    <t>0.9970,0.0013,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0020,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9942,0.0028,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0009,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9960,0.0013,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9921,0.0055,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9925,0.0021,0.0006,0.0023</t>
-  </si>
-  <si>
-    <t>0.0032,0.0058,0.9909,0.0027</t>
-  </si>
-  <si>
-    <t>0.0786,0.0139,0.9216,0.0018</t>
-  </si>
-  <si>
-    <t>0.4841,0.0123,0.4469,0.0677</t>
-  </si>
-  <si>
-    <t>0.1676,0.0019,0.8984,0.0016</t>
-  </si>
-  <si>
-    <t>0.0521,0.9431,0.0062,0.0012</t>
-  </si>
-  <si>
-    <t>0.0938,0.9084,0.0103,0.0012</t>
-  </si>
-  <si>
-    <t>0.2779,0.8079,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.2861,0.7679,0.0188,0.0016</t>
-  </si>
-  <si>
-    <t>0.1469,0.9114,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.0166,0.9795,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.5122,0.6108,0.0065,0.0011</t>
-  </si>
-  <si>
-    <t>0.7380,0.1009,0.1122,0.0167</t>
-  </si>
-  <si>
-    <t>0.1852,0.0020,0.9105,0.0007</t>
-  </si>
-  <si>
-    <t>0.4227,0.1990,0.3938,0.0140</t>
-  </si>
-  <si>
-    <t>0.5905,0.0743,0.4078,0.0262</t>
-  </si>
-  <si>
-    <t>0.0552,0.2367,0.0273,0.9292</t>
-  </si>
-  <si>
-    <t>0.0031,0.9911,0.0052,0.0011</t>
-  </si>
-  <si>
-    <t>0.0036,0.9794,0.0425,0.0265</t>
-  </si>
-  <si>
-    <t>0.0305,0.9414,0.0108,0.0509</t>
-  </si>
-  <si>
-    <t>0.0030,0.9212,0.8272,0.0019</t>
-  </si>
-  <si>
-    <t>0.0160,0.9756,0.0392,0.0002</t>
-  </si>
-  <si>
-    <t>0.6751,0.3972,0.0179,0.0009</t>
-  </si>
-  <si>
-    <t>0.6231,0.4813,0.0113,0.0015</t>
-  </si>
-  <si>
-    <t>0.9635,0.0115,0.0043,0.0178</t>
-  </si>
-  <si>
-    <t>0.9867,0.0029,0.0010,0.0057</t>
-  </si>
-  <si>
-    <t>0.9888,0.0049,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.9802,0.0106,0.0038,0.0031</t>
-  </si>
-  <si>
-    <t>0.9904,0.0038,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9685,0.0223,0.0079,0.0019</t>
-  </si>
-  <si>
-    <t>0.9661,0.0022,0.0009,0.0271</t>
-  </si>
-  <si>
-    <t>0.9882,0.0066,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.0046,0.7288,0.8683,0.0009</t>
-  </si>
-  <si>
-    <t>0.0098,0.6910,0.8365,0.0016</t>
-  </si>
-  <si>
-    <t>0.0032,0.3437,0.9511,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.2062,0.9721,0.0005</t>
-  </si>
-  <si>
-    <t>0.6977,0.0356,0.2775,0.0250</t>
-  </si>
-  <si>
-    <t>0.6573,0.0554,0.2959,0.0038</t>
-  </si>
-  <si>
-    <t>0.7117,0.0023,0.4173,0.0036</t>
-  </si>
-  <si>
-    <t>0.5443,0.0730,0.3993,0.0045</t>
-  </si>
-  <si>
-    <t>0.0161,0.0127,0.0037,0.9896</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.0070,0.9962</t>
-  </si>
-  <si>
-    <t>0.0031,0.0389,0.0026,0.9960</t>
-  </si>
-  <si>
-    <t>0.0078,0.0006,0.0021,0.9945</t>
-  </si>
-  <si>
-    <t>0.0282,0.8610,0.3200,0.0108</t>
-  </si>
-  <si>
-    <t>0.9862,0.0091,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.2969,0.6988,0.0385,0.0032</t>
-  </si>
-  <si>
-    <t>0.9391,0.0347,0.0037,0.0241</t>
-  </si>
-  <si>
-    <t>0.9097,0.1033,0.0207,0.0037</t>
-  </si>
-  <si>
-    <t>0.9793,0.0035,0.0019,0.0072</t>
-  </si>
-  <si>
-    <t>0.0467,0.0194,0.0177,0.9630</t>
-  </si>
-  <si>
-    <t>0.9691,0.0150,0.0065,0.0044</t>
-  </si>
-  <si>
-    <t>0.0007,0.0377,0.9888,0.0115</t>
-  </si>
-  <si>
-    <t>0.9351,0.0053,0.0100,0.0404</t>
-  </si>
-  <si>
-    <t>0.8796,0.0203,0.0121,0.0902</t>
-  </si>
-  <si>
-    <t>0.6430,0.3089,0.0460,0.0515</t>
-  </si>
-  <si>
-    <t>0.9029,0.0395,0.0272,0.0082</t>
-  </si>
-  <si>
-    <t>0.8258,0.1340,0.0555,0.0054</t>
-  </si>
-  <si>
-    <t>0.2348,0.6362,0.1832,0.0274</t>
-  </si>
-  <si>
-    <t>0.8316,0.0542,0.1270,0.0085</t>
-  </si>
-  <si>
-    <t>0.5690,0.3488,0.0904,0.0391</t>
-  </si>
-  <si>
-    <t>0.9925,0.0044,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9853,0.0082,0.0014,0.0022</t>
-  </si>
-  <si>
-    <t>0.9878,0.0052,0.0008,0.0030</t>
-  </si>
-  <si>
-    <t>0.9894,0.0024,0.0020,0.0023</t>
-  </si>
-  <si>
-    <t>0.9747,0.0115,0.0073,0.0027</t>
-  </si>
-  <si>
-    <t>0.9644,0.0132,0.0007,0.0115</t>
-  </si>
-  <si>
-    <t>0.9671,0.0162,0.0078,0.0060</t>
-  </si>
-  <si>
-    <t>0.9767,0.0061,0.0019,0.0093</t>
-  </si>
-  <si>
-    <t>0.5166,0.5638,0.0011,0.0020</t>
-  </si>
-  <si>
-    <t>0.7049,0.3763,0.0189,0.0007</t>
-  </si>
-  <si>
-    <t>0.6817,0.2376,0.1138,0.0114</t>
-  </si>
-  <si>
-    <t>0.3573,0.2041,0.6116,0.0143</t>
-  </si>
-  <si>
-    <t>0.9328,0.0529,0.0115,0.0099</t>
-  </si>
-  <si>
-    <t>0.7837,0.2932,0.0214,0.0036</t>
-  </si>
-  <si>
-    <t>0.8890,0.1502,0.0091,0.0034</t>
-  </si>
-  <si>
-    <t>0.9453,0.0742,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.0219,0.9930,0.0012</t>
-  </si>
-  <si>
-    <t>0.9562,0.0409,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.0048,0.0178,0.9912,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.0589,0.9843,0.0042</t>
-  </si>
-  <si>
-    <t>0.0355,0.0028,0.9807,0.0004</t>
-  </si>
-  <si>
-    <t>0.0122,0.0982,0.9674,0.0027</t>
-  </si>
-  <si>
-    <t>0.0059,0.0095,0.9891,0.0020</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.9959,0.0009</t>
-  </si>
-  <si>
-    <t>0.0281,0.0011,0.9859,0.0005</t>
-  </si>
-  <si>
-    <t>0.4978,0.0152,0.5795,0.0106</t>
-  </si>
-  <si>
-    <t>0.4276,0.0073,0.6861,0.0072</t>
-  </si>
-  <si>
-    <t>0.7160,0.0463,0.2688,0.0188</t>
-  </si>
-  <si>
-    <t>0.2464,0.1103,0.6281,0.0034</t>
-  </si>
-  <si>
-    <t>0.4154,0.0316,0.6296,0.0020</t>
-  </si>
-  <si>
-    <t>0.4352,0.0647,0.4532,0.0023</t>
-  </si>
-  <si>
-    <t>0.4466,0.0074,0.6583,0.0072</t>
-  </si>
-  <si>
-    <t>0.3731,0.0503,0.6101,0.0377</t>
-  </si>
-  <si>
-    <t>0.9088,0.1572,0.0081,0.0013</t>
-  </si>
-  <si>
-    <t>0.5907,0.5542,0.0096,0.0013</t>
-  </si>
-  <si>
-    <t>0.6027,0.5716,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9664,0.0320,0.0065,0.0015</t>
-  </si>
-  <si>
-    <t>0.9458,0.0803,0.0062,0.0019</t>
-  </si>
-  <si>
-    <t>0.6149,0.1330,0.2823,0.0263</t>
-  </si>
-  <si>
-    <t>0.7482,0.0197,0.2457,0.0202</t>
-  </si>
-  <si>
-    <t>0.7072,0.0131,0.2594,0.0265</t>
-  </si>
-  <si>
-    <t>0.5717,0.0209,0.4303,0.0208</t>
-  </si>
-  <si>
-    <t>0.7248,0.0234,0.2868,0.0157</t>
-  </si>
-  <si>
-    <t>0.0220,0.0308,0.9440,0.0238</t>
-  </si>
-  <si>
-    <t>0.0069,0.4174,0.9170,0.0020</t>
-  </si>
-  <si>
-    <t>0.1242,0.1283,0.8046,0.0142</t>
-  </si>
-  <si>
-    <t>0.0332,0.0282,0.9585,0.0047</t>
-  </si>
-  <si>
-    <t>0.0172,0.0446,0.9544,0.0060</t>
-  </si>
-  <si>
-    <t>0.9872,0.0075,0.0007,0.0021</t>
-  </si>
-  <si>
-    <t>0.9727,0.0260,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.9886,0.0090,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9899,0.0071,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9845,0.0102,0.0019,0.0021</t>
-  </si>
-  <si>
-    <t>0.9831,0.0201,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9862,0.0018,0.0001,0.0074</t>
-  </si>
-  <si>
-    <t>0.9821,0.0084,0.0044,0.0029</t>
-  </si>
-  <si>
-    <t>0.2666,0.0402,0.7555,0.0182</t>
-  </si>
-  <si>
-    <t>0.2842,0.5366,0.3411,0.0180</t>
-  </si>
-  <si>
-    <t>0.6567,0.0017,0.0677,0.1574</t>
-  </si>
-  <si>
-    <t>0.0357,0.0142,0.9593,0.0043</t>
-  </si>
-  <si>
-    <t>0.0017,0.0338,0.9896,0.0022</t>
-  </si>
-  <si>
-    <t>0.0262,0.0977,0.9312,0.0047</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.0387,0.0116,0.9553,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.0536,0.9940,0.0003</t>
-  </si>
-  <si>
-    <t>0.0074,0.0048,0.9914,0.0008</t>
-  </si>
-  <si>
-    <t>0.2478,0.0382,0.7426,0.0080</t>
-  </si>
-  <si>
-    <t>0.5953,0.0241,0.4192,0.0147</t>
-  </si>
-  <si>
-    <t>0.7016,0.0065,0.3989,0.0017</t>
-  </si>
-  <si>
-    <t>0.6773,0.0254,0.2858,0.0379</t>
-  </si>
-  <si>
-    <t>0.9861,0.0078,0.0008,0.0023</t>
-  </si>
-  <si>
-    <t>0.9945,0.0024,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9891,0.0076,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9874,0.0161,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9835,0.0098,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.9781,0.0193,0.0030,0.0028</t>
-  </si>
-  <si>
-    <t>0.9910,0.0123,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9781,0.0147,0.0013,0.0026</t>
-  </si>
-  <si>
-    <t>0.0224,0.0041,0.9806,0.0007</t>
-  </si>
-  <si>
-    <t>0.0237,0.0464,0.9473,0.0115</t>
-  </si>
-  <si>
-    <t>0.0231,0.0210,0.9630,0.0048</t>
-  </si>
-  <si>
-    <t>0.0842,0.3615,0.5913,0.0138</t>
-  </si>
-  <si>
-    <t>0.0096,0.0455,0.9672,0.0096</t>
-  </si>
-  <si>
-    <t>0.2570,0.0196,0.7423,0.0328</t>
-  </si>
-  <si>
-    <t>0.0598,0.0862,0.7476,0.1864</t>
-  </si>
-  <si>
-    <t>0.0205,0.0257,0.9589,0.0090</t>
-  </si>
-  <si>
-    <t>0.8427,0.0061,0.0111,0.1392</t>
-  </si>
-  <si>
-    <t>0.2467,0.0314,0.0043,0.8663</t>
-  </si>
-  <si>
-    <t>0.0527,0.0087,0.0081,0.9671</t>
-  </si>
-  <si>
-    <t>0.0010,0.0014,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0158,0.0014,0.0056,0.9872</t>
-  </si>
-  <si>
-    <t>0.6814,0.1457,0.0622,0.1910</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.5980,0.1031,0.2512,0.2022</t>
+  </si>
+  <si>
+    <t>0.0189,0.0026,0.0002,0.9938</t>
+  </si>
+  <si>
+    <t>0.3836,0.1313,0.0182,0.6751</t>
+  </si>
+  <si>
+    <t>0.0116,0.0016,0.0029,0.9930</t>
+  </si>
+  <si>
+    <t>0.9940,0.0040,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0063,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9852,0.0128,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9948,0.0021,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0056,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9886,0.0104,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9892,0.0055,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.6804,0.0057,0.2464,0.0330</t>
+  </si>
+  <si>
+    <t>0.2719,0.0500,0.6908,0.0081</t>
+  </si>
+  <si>
+    <t>0.4524,0.0102,0.6512,0.0014</t>
+  </si>
+  <si>
+    <t>0.4738,0.0050,0.6868,0.0022</t>
+  </si>
+  <si>
+    <t>0.6601,0.0246,0.3352,0.0361</t>
+  </si>
+  <si>
+    <t>0.0214,0.9763,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0780,0.9311,0.0080,0.0005</t>
+  </si>
+  <si>
+    <t>0.1366,0.8830,0.0051,0.0021</t>
+  </si>
+  <si>
+    <t>0.1263,0.9152,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.9958,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.3195,0.0088,0.7631,0.0038</t>
+  </si>
+  <si>
+    <t>0.1006,0.0222,0.8329,0.0552</t>
+  </si>
+  <si>
+    <t>0.0253,0.0158,0.9617,0.0144</t>
+  </si>
+  <si>
+    <t>0.3996,0.0024,0.4743,0.0519</t>
+  </si>
+  <si>
+    <t>0.0253,0.0253,0.9483,0.0198</t>
+  </si>
+  <si>
+    <t>0.0466,0.0045,0.9581,0.0046</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9884,0.0417</t>
+  </si>
+  <si>
+    <t>0.5113,0.4122,0.0788,0.0054</t>
+  </si>
+  <si>
+    <t>0.5741,0.2088,0.2753,0.0124</t>
+  </si>
+  <si>
+    <t>0.0004,0.0165,0.9972,0.0011</t>
+  </si>
+  <si>
+    <t>0.0091,0.9444,0.2180,0.0017</t>
+  </si>
+  <si>
+    <t>0.6855,0.2210,0.1586,0.0559</t>
+  </si>
+  <si>
+    <t>0.2197,0.1573,0.5562,0.0016</t>
+  </si>
+  <si>
+    <t>0.8343,0.2292,0.0139,0.0012</t>
+  </si>
+  <si>
+    <t>0.0237,0.9148,0.4015,0.0014</t>
+  </si>
+  <si>
+    <t>0.0638,0.7266,0.5334,0.0195</t>
+  </si>
+  <si>
+    <t>0.0186,0.3327,0.9214,0.0068</t>
+  </si>
+  <si>
+    <t>0.0200,0.1157,0.9408,0.0058</t>
+  </si>
+  <si>
+    <t>0.1037,0.0253,0.8116,0.0637</t>
+  </si>
+  <si>
+    <t>0.0041,0.1495,0.9746,0.0008</t>
+  </si>
+  <si>
+    <t>0.0048,0.9548,0.1568,0.0031</t>
+  </si>
+  <si>
+    <t>0.0359,0.0115,0.9562,0.0077</t>
+  </si>
+  <si>
+    <t>0.0059,0.9352,0.0172,0.5239</t>
+  </si>
+  <si>
+    <t>0.0224,0.9237,0.0381,0.0931</t>
+  </si>
+  <si>
+    <t>0.0026,0.9802,0.1383,0.0007</t>
+  </si>
+  <si>
+    <t>0.0049,0.9825,0.0792,0.0020</t>
+  </si>
+  <si>
+    <t>0.0019,0.0273,0.9892,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.2118,0.9875,0.0013</t>
+  </si>
+  <si>
+    <t>0.2022,0.0614,0.6872,0.0879</t>
+  </si>
+  <si>
+    <t>0.0195,0.0029,0.9828,0.0009</t>
+  </si>
+  <si>
+    <t>0.0018,0.0024,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0069,0.0396,0.9826,0.0008</t>
+  </si>
+  <si>
+    <t>0.9257,0.1074,0.0073,0.0016</t>
+  </si>
+  <si>
+    <t>0.9867,0.0067,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9379,0.0068,0.0074,0.0389</t>
+  </si>
+  <si>
+    <t>0.0014,0.2946,0.9888,0.0003</t>
+  </si>
+  <si>
+    <t>0.9761,0.0226,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.9849,0.0165,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9636,0.0625,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.6634,0.9195,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0156,0.9976,0.0004</t>
+  </si>
+  <si>
+    <t>0.0035,0.0073,0.9890,0.0045</t>
+  </si>
+  <si>
+    <t>0.0010,0.8758,0.9196,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0741,0.9159,0.0209,0.0007</t>
+  </si>
+  <si>
+    <t>0.0065,0.9899,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.9100,0.0209,0.0554,0.0021</t>
+  </si>
+  <si>
+    <t>0.1867,0.0988,0.7698,0.0039</t>
+  </si>
+  <si>
+    <t>0.0179,0.0892,0.9157,0.0087</t>
+  </si>
+  <si>
+    <t>0.0003,0.8088,0.9655,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.8930,0.9189,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9929,0.1522,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9583,0.8555,0.0002</t>
+  </si>
+  <si>
+    <t>0.0659,0.0032,0.0980,0.8480</t>
+  </si>
+  <si>
+    <t>0.0101,0.0009,0.0004,0.9964</t>
+  </si>
+  <si>
+    <t>0.0567,0.0541,0.0014,0.9701</t>
+  </si>
+  <si>
+    <t>0.0066,0.0050,0.0026,0.9949</t>
+  </si>
+  <si>
+    <t>0.0036,0.0011,0.0185,0.9885</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.0008,0.9198,0.9035,0.0002</t>
+  </si>
+  <si>
+    <t>0.0032,0.6178,0.9380,0.0006</t>
+  </si>
+  <si>
+    <t>0.0145,0.5770,0.8053,0.0036</t>
+  </si>
+  <si>
+    <t>0.0036,0.8126,0.8602,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9743,0.7526,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.7735,0.8097,0.0003</t>
+  </si>
+  <si>
+    <t>0.9876,0.0091,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9833,0.0132,0.0023,0.0019</t>
+  </si>
+  <si>
+    <t>0.9863,0.0112,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9906,0.0067,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9747,0.0191,0.0049,0.0026</t>
+  </si>
+  <si>
+    <t>0.9915,0.0068,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9821,0.0148,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9744,0.0264,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9952,0.0044,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0068,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0024,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9930,0.0029,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9938,0.0016,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9943,0.0041,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0028,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9909,0.0060,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.0264,0.9965,0.0012</t>
+  </si>
+  <si>
+    <t>0.1505,0.0175,0.8566,0.0057</t>
+  </si>
+  <si>
+    <t>0.5263,0.0033,0.5012,0.0190</t>
+  </si>
+  <si>
+    <t>0.1475,0.0037,0.8906,0.0093</t>
+  </si>
+  <si>
+    <t>0.0226,0.9699,0.0067,0.0007</t>
+  </si>
+  <si>
+    <t>0.0745,0.9254,0.0075,0.0031</t>
+  </si>
+  <si>
+    <t>0.0215,0.9748,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.0756,0.9192,0.0064,0.0035</t>
+  </si>
+  <si>
+    <t>0.0596,0.9326,0.0115,0.0012</t>
+  </si>
+  <si>
+    <t>0.2333,0.8340,0.0062,0.0006</t>
+  </si>
+  <si>
+    <t>0.4857,0.6252,0.0087,0.0003</t>
+  </si>
+  <si>
+    <t>0.6949,0.1688,0.1615,0.0499</t>
+  </si>
+  <si>
+    <t>0.1059,0.1111,0.8298,0.0137</t>
+  </si>
+  <si>
+    <t>0.3854,0.3656,0.2526,0.0127</t>
+  </si>
+  <si>
+    <t>0.6165,0.0389,0.3809,0.0233</t>
+  </si>
+  <si>
+    <t>0.4291,0.0420,0.4608,0.1879</t>
+  </si>
+  <si>
+    <t>0.0149,0.9715,0.0175,0.0032</t>
+  </si>
+  <si>
+    <t>0.0021,0.9770,0.0392,0.0407</t>
+  </si>
+  <si>
+    <t>0.0082,0.9817,0.0084,0.0036</t>
+  </si>
+  <si>
+    <t>0.0002,0.9373,0.9514,0.0003</t>
+  </si>
+  <si>
+    <t>0.0335,0.9595,0.0200,0.0004</t>
+  </si>
+  <si>
+    <t>0.5389,0.4837,0.0369,0.0015</t>
+  </si>
+  <si>
+    <t>0.5473,0.5304,0.0174,0.0006</t>
+  </si>
+  <si>
+    <t>0.9747,0.0142,0.0050,0.0030</t>
+  </si>
+  <si>
+    <t>0.9718,0.0102,0.0027,0.0128</t>
+  </si>
+  <si>
+    <t>0.9902,0.0045,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9784,0.0125,0.0052,0.0020</t>
+  </si>
+  <si>
+    <t>0.9951,0.0032,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9433,0.0625,0.0069,0.0034</t>
+  </si>
+  <si>
+    <t>0.9774,0.0114,0.0063,0.0034</t>
+  </si>
+  <si>
+    <t>0.9894,0.0028,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.0229,0.4309,0.8660,0.0023</t>
+  </si>
+  <si>
+    <t>0.0119,0.3470,0.8624,0.0006</t>
+  </si>
+  <si>
+    <t>0.0060,0.7613,0.7171,0.0005</t>
+  </si>
+  <si>
+    <t>0.0133,0.0803,0.9425,0.0002</t>
+  </si>
+  <si>
+    <t>0.4852,0.1678,0.3263,0.1862</t>
+  </si>
+  <si>
+    <t>0.7944,0.0323,0.1568,0.0183</t>
+  </si>
+  <si>
+    <t>0.6772,0.0064,0.4233,0.0045</t>
+  </si>
+  <si>
+    <t>0.4731,0.0544,0.5167,0.0258</t>
+  </si>
+  <si>
+    <t>0.0239,0.0024,0.0051,0.9847</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0018,0.9983</t>
+  </si>
+  <si>
+    <t>0.0009,0.0223,0.0237,0.9924</t>
+  </si>
+  <si>
+    <t>0.0240,0.0018,0.0053,0.9841</t>
+  </si>
+  <si>
+    <t>0.0031,0.8303,0.8247,0.0007</t>
+  </si>
+  <si>
+    <t>0.9764,0.0146,0.0038,0.0035</t>
+  </si>
+  <si>
+    <t>0.6985,0.3778,0.0216,0.0035</t>
+  </si>
+  <si>
+    <t>0.9820,0.0039,0.0023,0.0067</t>
+  </si>
+  <si>
+    <t>0.9621,0.0367,0.0066,0.0023</t>
+  </si>
+  <si>
+    <t>0.9568,0.0059,0.0261,0.0055</t>
+  </si>
+  <si>
+    <t>0.1268,0.0696,0.0221,0.9210</t>
+  </si>
+  <si>
+    <t>0.9738,0.0087,0.0062,0.0060</t>
+  </si>
+  <si>
+    <t>0.0035,0.0860,0.9551,0.0501</t>
+  </si>
+  <si>
+    <t>0.8996,0.0035,0.0105,0.0651</t>
+  </si>
+  <si>
+    <t>0.9269,0.0068,0.0246,0.0203</t>
+  </si>
+  <si>
+    <t>0.3711,0.6949,0.0283,0.0054</t>
+  </si>
+  <si>
+    <t>0.9023,0.0249,0.0470,0.0080</t>
+  </si>
+  <si>
+    <t>0.7919,0.2179,0.0127,0.0142</t>
+  </si>
+  <si>
+    <t>0.2357,0.7612,0.0231,0.0326</t>
+  </si>
+  <si>
+    <t>0.7625,0.1045,0.1303,0.0027</t>
+  </si>
+  <si>
+    <t>0.6903,0.2480,0.1080,0.0314</t>
+  </si>
+  <si>
+    <t>0.9886,0.0082,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9756,0.0039,0.0005,0.0206</t>
+  </si>
+  <si>
+    <t>0.9792,0.0104,0.0038,0.0037</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9828,0.0056,0.0030,0.0042</t>
+  </si>
+  <si>
+    <t>0.9768,0.0087,0.0049,0.0061</t>
+  </si>
+  <si>
+    <t>0.9872,0.0072,0.0009,0.0022</t>
+  </si>
+  <si>
+    <t>0.9884,0.0065,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.6295,0.4509,0.0047,0.0056</t>
+  </si>
+  <si>
+    <t>0.4454,0.6298,0.0258,0.0007</t>
+  </si>
+  <si>
+    <t>0.7084,0.4220,0.0059,0.0033</t>
+  </si>
+  <si>
+    <t>0.1049,0.1220,0.8580,0.0199</t>
+  </si>
+  <si>
+    <t>0.9840,0.0115,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.8420,0.1652,0.0300,0.0022</t>
+  </si>
+  <si>
+    <t>0.9796,0.0287,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9618,0.0353,0.0071,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0105,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.9223,0.0855,0.0110,0.0064</t>
+  </si>
+  <si>
+    <t>0.0153,0.0017,0.9876,0.0007</t>
+  </si>
+  <si>
+    <t>0.0045,0.4051,0.9545,0.0033</t>
+  </si>
+  <si>
+    <t>0.2900,0.0039,0.8460,0.0009</t>
+  </si>
+  <si>
+    <t>0.0038,0.1409,0.9774,0.0002</t>
+  </si>
+  <si>
+    <t>0.0375,0.0224,0.9537,0.0049</t>
+  </si>
+  <si>
+    <t>0.0023,0.0013,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0099,0.0032,0.9899,0.0008</t>
+  </si>
+  <si>
+    <t>0.3336,0.0146,0.7232,0.0060</t>
+  </si>
+  <si>
+    <t>0.5180,0.0189,0.5448,0.0077</t>
+  </si>
+  <si>
+    <t>0.3006,0.0201,0.7435,0.0048</t>
+  </si>
+  <si>
+    <t>0.0674,0.3686,0.6326,0.0031</t>
+  </si>
+  <si>
+    <t>0.0432,0.7585,0.3890,0.0041</t>
+  </si>
+  <si>
+    <t>0.5738,0.0982,0.3136,0.0028</t>
+  </si>
+  <si>
+    <t>0.5622,0.0560,0.4277,0.0190</t>
+  </si>
+  <si>
+    <t>0.2701,0.0893,0.6624,0.0112</t>
+  </si>
+  <si>
+    <t>0.9489,0.0968,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.5180,0.6795,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8297,0.2866,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.9799,0.0190,0.0029,0.0011</t>
+  </si>
+  <si>
+    <t>0.9293,0.1253,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.7131,0.0509,0.2622,0.0109</t>
+  </si>
+  <si>
+    <t>0.8252,0.0082,0.1624,0.0091</t>
+  </si>
+  <si>
+    <t>0.6585,0.0115,0.1719,0.0793</t>
+  </si>
+  <si>
+    <t>0.4444,0.0287,0.5625,0.0111</t>
+  </si>
+  <si>
+    <t>0.5806,0.0144,0.4286,0.0280</t>
+  </si>
+  <si>
+    <t>0.0112,0.0181,0.9682,0.0157</t>
+  </si>
+  <si>
+    <t>0.0231,0.6594,0.6988,0.0058</t>
+  </si>
+  <si>
+    <t>0.0495,0.0505,0.9179,0.0112</t>
+  </si>
+  <si>
+    <t>0.0549,0.0758,0.9127,0.0116</t>
+  </si>
+  <si>
+    <t>0.0432,0.2000,0.8453,0.0047</t>
+  </si>
+  <si>
+    <t>0.9894,0.0051,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9818,0.0110,0.0022,0.0028</t>
+  </si>
+  <si>
+    <t>0.9794,0.0068,0.0008,0.0068</t>
+  </si>
+  <si>
+    <t>0.9811,0.0267,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9866,0.0106,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9891,0.0058,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9883,0.0054,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9897,0.0041,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.0650,0.0175,0.9048,0.0487</t>
+  </si>
+  <si>
+    <t>0.4773,0.2876,0.3735,0.0480</t>
+  </si>
+  <si>
+    <t>0.8612,0.0849,0.0547,0.0117</t>
+  </si>
+  <si>
+    <t>0.0043,0.0087,0.9931,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0254,0.9886,0.0042</t>
+  </si>
+  <si>
+    <t>0.0051,0.1135,0.9730,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9993,0.0010</t>
+  </si>
+  <si>
+    <t>0.1838,0.0017,0.9058,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0029,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0506,0.0040,0.9582,0.0039</t>
+  </si>
+  <si>
+    <t>0.0608,0.0429,0.9166,0.0022</t>
+  </si>
+  <si>
+    <t>0.4906,0.0084,0.6180,0.0069</t>
+  </si>
+  <si>
+    <t>0.7531,0.0038,0.3438,0.0031</t>
+  </si>
+  <si>
+    <t>0.8265,0.0023,0.2448,0.0021</t>
+  </si>
+  <si>
+    <t>0.9618,0.0306,0.0052,0.0032</t>
+  </si>
+  <si>
+    <t>0.9916,0.0058,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0066,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9883,0.0097,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9880,0.0037,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9689,0.0167,0.0044,0.0067</t>
+  </si>
+  <si>
+    <t>0.9880,0.0091,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9793,0.0079,0.0011,0.0055</t>
+  </si>
+  <si>
+    <t>0.1108,0.0605,0.8281,0.0177</t>
+  </si>
+  <si>
+    <t>0.0067,0.2455,0.9545,0.0016</t>
+  </si>
+  <si>
+    <t>0.0204,0.0932,0.9409,0.0091</t>
+  </si>
+  <si>
+    <t>0.0647,0.1054,0.8479,0.0029</t>
+  </si>
+  <si>
+    <t>0.0018,0.0214,0.9934,0.0008</t>
+  </si>
+  <si>
+    <t>0.2365,0.0060,0.2602,0.3591</t>
+  </si>
+  <si>
+    <t>0.3506,0.0295,0.6669,0.0087</t>
+  </si>
+  <si>
+    <t>0.0700,0.0629,0.8827,0.0393</t>
+  </si>
+  <si>
+    <t>0.8116,0.0075,0.0457,0.1016</t>
+  </si>
+  <si>
+    <t>0.0236,0.0067,0.0145,0.9787</t>
+  </si>
+  <si>
+    <t>0.0062,0.0008,0.0015,0.9960</t>
+  </si>
+  <si>
+    <t>0.0047,0.0010,0.0002,0.9979</t>
+  </si>
+  <si>
+    <t>0.0019,0.0009,0.0009,0.9982</t>
+  </si>
+  <si>
+    <t>0.5206,0.0299,0.0133,0.6199</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1996,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2318,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2444,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2937,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3133,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3438,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3553,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3872,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3900,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3931,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4211,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4407,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4614,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4645,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4684,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4740,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4866,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5188,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
